--- a/Code/Jupiter/Connect4/Kaggle games.xlsx
+++ b/Code/Jupiter/Connect4/Kaggle games.xlsx
@@ -5,11 +5,16 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="LA" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="PPO" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">LA!$A$1:$M$14</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">PPO!$A$1:$D$3</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -20,30 +25,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t xml:space="preserve">Game</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+  <si>
+    <t xml:space="preserve">submission</t>
   </si>
   <si>
     <t xml:space="preserve">score</t>
   </si>
   <si>
-    <t xml:space="preserve">Depth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defensive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floating near</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floating far</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parity bonus</t>
+    <t xml:space="preserve">depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-7 (base) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-7 (D1.55, TS9) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-7 (D1.5 FN0.25 FF0.075 C7 PB1.0 V0.7 T0.5 PM0.3 PU0.2 TS0.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-13 (C3) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-11 (D1.55, TS9) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-9 (D1.55, TS9) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-9 (D1.60) (D1.60 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-9 (C8) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-9 (base) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-8 () (D1.60 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-9 (D1.50) (D1.50 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bbLA-5 (D1.55, TS9) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tactics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_14 (POC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_14 - win-now + must-block (1-ply only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">win-now + must-block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">+handover fltr</t>
   </si>
 </sst>
 </file>
@@ -132,11 +209,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -149,6 +226,23 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF729FCF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -210,6 +304,14 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -323,54 +425,660 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="82.17"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>850</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>837</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>817</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>805</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>793</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>785</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>770</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>767</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>759</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>743</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>713</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>688</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>667</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M14"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Navadno"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.39"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>261</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D3"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -378,5 +1086,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Navadno"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Navadno"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Code/Jupiter/Connect4/Kaggle games.xlsx
+++ b/Code/Jupiter/Connect4/Kaggle games.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="LA" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t xml:space="preserve">submission</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t xml:space="preserve">win-now + must-block </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_14 (handover filter)</t>
   </si>
   <si>
     <t xml:space="preserve">+handover fltr</t>
@@ -477,7 +480,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>850</v>
+        <v>831</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>7</v>
@@ -1049,7 +1052,7 @@
         <v>27</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -1060,7 +1063,7 @@
         <v>29</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>28</v>
@@ -1070,11 +1073,14 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Kaggle games.xlsx
+++ b/Code/Jupiter/Connect4/Kaggle games.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t xml:space="preserve">submission</t>
   </si>
@@ -114,6 +114,9 @@
     <t xml:space="preserve">PPO_14</t>
   </si>
   <si>
+    <t xml:space="preserve">none</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPO_14 - win-now + must-block (1-ply only)</t>
   </si>
   <si>
@@ -124,6 +127,12 @@
   </si>
   <si>
     <t xml:space="preserve">+handover fltr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_14 (DT guard)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+DT guard</t>
   </si>
 </sst>
 </file>
@@ -480,7 +489,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>7</v>
@@ -1026,7 +1035,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.7"/>
@@ -1057,10 +1066,13 @@
       <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>380</v>
@@ -1069,18 +1081,35 @@
         <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>122</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Code/Jupiter/Connect4/Kaggle games.xlsx
+++ b/Code/Jupiter/Connect4/Kaggle games.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="LA" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="PPO" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">LA!$A$1:$M$14</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">PPO!$A$1:$D$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">LA!$A$1:$M$16</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">PPO!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="45">
   <si>
     <t xml:space="preserve">submission</t>
   </si>
@@ -66,18 +66,21 @@
     <t xml:space="preserve">TS</t>
   </si>
   <si>
+    <t xml:space="preserve">bbLA-7 (D1.55, TS9) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
     <t xml:space="preserve">bbLA-7 (base) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
   </si>
   <si>
-    <t xml:space="preserve">bbLA-7 (D1.55, TS9) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
-  </si>
-  <si>
     <t xml:space="preserve">bbLA-7 (D1.5 FN0.25 FF0.075 C7 PB1.0 V0.7 T0.5 PM0.3 PU0.2 TS0.55)</t>
   </si>
   <si>
     <t xml:space="preserve">bbLA-13 (C3) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
   </si>
   <si>
+    <t xml:space="preserve">bbLA-7 (FF FN 2x) (D1.55 FN0.5 FF0.25 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
     <t xml:space="preserve">bbLA-11 (D1.55, TS9) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
   </si>
   <si>
@@ -102,45 +105,70 @@
     <t xml:space="preserve">bbLA-5 (D1.55, TS9) (D1.55 FN0.25 FF0.125 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
   </si>
   <si>
+    <t xml:space="preserve">bbLA-7 (FF FN 0) (D1.55 FN0 FF0 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> bbLA-7 (FF2x) (D1.55 FN0.5 FF0.25 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> bbLA-7 (FF0.2 FN0) (D1.55 FN0.0 FF0.2 C3 PB0.75 V0.8 T75 PM0.5 PU0.25 TS9)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Model</t>
   </si>
   <si>
+    <t xml:space="preserve">ELO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GS</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tactics</t>
   </si>
   <si>
-    <t xml:space="preserve">PPO_14 (POC)</t>
+    <t xml:space="preserve">PPO_14_DT</t>
   </si>
   <si>
     <t xml:space="preserve">PPO_14</t>
   </si>
   <si>
-    <t xml:space="preserve">none</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_14 - win-now + must-block (1-ply only)</t>
+    <t xml:space="preserve">win-now + must-block + handover + DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_404_DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">win-now + must-block + handover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_403</t>
   </si>
   <si>
     <t xml:space="preserve">win-now + must-block </t>
   </si>
   <si>
-    <t xml:space="preserve">PPO_14 (handover filter)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+handover fltr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_14 (DT guard)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+DT guard</t>
+    <t xml:space="preserve">PPO_415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_408</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -216,7 +244,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -226,6 +254,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,7 +469,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="82.17"/>
@@ -489,7 +521,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>7</v>
@@ -530,7 +562,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>7</v>
@@ -653,19 +685,19 @@
         <v>17</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>1.55</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>3</v>
@@ -694,10 +726,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>1.55</v>
@@ -735,13 +767,13 @@
         <v>19</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>0.25</v>
@@ -776,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>0.25</v>
@@ -791,7 +823,7 @@
         <v>0.125</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>0.75</v>
@@ -817,7 +849,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>9</v>
@@ -832,7 +864,7 @@
         <v>0.125</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>0.75</v>
@@ -858,10 +890,10 @@
         <v>22</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>1.55</v>
@@ -899,10 +931,10 @@
         <v>23</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>713</v>
+        <v>743</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1.55</v>
@@ -937,16 +969,16 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>9</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>0.25</v>
@@ -981,13 +1013,13 @@
         <v>24</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>0.25</v>
@@ -1017,8 +1049,213 @@
         <v>9</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>667</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>518</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>768</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>681</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>757</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M16"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1035,11 +1272,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="27.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1050,70 +1289,220 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>240</v>
+        <v>551</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1079.59190609549</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.176302414226163</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>380</v>
+        <v>520</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1055.88655528494</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.180376722331662</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>122</v>
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>491</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1079.59190609549</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.176302414226163</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>488</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1070.27063811779</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.11693348529805</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>487</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1055.88655528494</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.180376722331662</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>434</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1087.5054634966</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.180376722331662</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>434</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>983.162481028837</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.116652782690413</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>428</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1043.75022781835</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.186072722947944</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="0" t="n">
-        <v>83</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>35</v>
+      <c r="B10" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1079.59190609549</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.176302414226163</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>369</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>911.802288675888</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.0548309033993906</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
+  <autoFilter ref="A1:F11"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/Code/Jupiter/Connect4/Kaggle games.xlsx
+++ b/Code/Jupiter/Connect4/Kaggle games.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">LA!$A$1:$M$16</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">PPO!$A$1:$F$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">PPO!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t xml:space="preserve">submission</t>
   </si>
@@ -126,6 +126,12 @@
     <t xml:space="preserve">Tactics</t>
   </si>
   <si>
+    <t xml:space="preserve">PPO_703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPO_14_DT</t>
   </si>
   <si>
@@ -135,31 +141,19 @@
     <t xml:space="preserve">win-now + must-block + handover + DT</t>
   </si>
   <si>
+    <t xml:space="preserve">PPO_702GS</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPO_404_DT</t>
   </si>
   <si>
     <t xml:space="preserve">PPO_404</t>
   </si>
   <si>
-    <t xml:space="preserve">win-now + must-block + handover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">win-now + must-block </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPO_408</t>
+    <t xml:space="preserve">PPO_701_DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPO_701</t>
   </si>
 </sst>
 </file>
@@ -1272,13 +1266,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="27.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="48.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1306,59 +1300,59 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>1115</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>1079.59190609549</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.176302414226163</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>510</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>520</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="3" t="n">
+        <v>1079.59190609549</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.176302414226163</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>1055.88655528494</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.180376722331662</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>504</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>1074</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>491</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>1079.59190609549</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.176302414226163</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1366,143 +1360,43 @@
         <v>39</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1070.27063811779</v>
+        <v>1055.88655528494</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.11693348529805</v>
+        <v>0.180376722331662</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1055.88655528494</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.180376722331662</v>
+        <v>42</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>1057</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>434</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1087.5054634966</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.180376722331662</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>434</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>983.162481028837</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.116652782690413</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>428</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>1043.75022781835</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.186072722947944</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>420</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1079.59190609549</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.176302414226163</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>369</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>911.802288675888</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.0548309033993906</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>41</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:F6"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
